--- a/machines_csv.xlsx
+++ b/machines_csv.xlsx
@@ -1075,6 +1075,7 @@
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="39.140625" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
